--- a/frontend/public/ejemplos/ppe_propiedad_planta/RQ-003_prestamos.xlsx
+++ b/frontend/public/ejemplos/ppe_propiedad_planta/RQ-003_prestamos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léame" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,60 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+    </font>
+    <font>
+      <color rgb="006B7280"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +87,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,158 +494,168 @@
   </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N° de préstamo o contrato</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Tipo (Específico / General)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Activo u obra financiada (solo los específicos)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Importe del préstamo vigente en el período</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Tasa nominal anual (%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Costo financiero del período realmente incurrido</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Rendimientos de la inversión temporal de esos fondos (solo los específicos)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>PR-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Específico</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Banco del Pacífico · nave industrial</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>120000</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>PR-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Banco Pichincha · capital de trabajo</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>400000</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>32000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PR-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Produbanco · línea de crédito</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -580,36 +668,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>AuditConsulting Auditores Cía. Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Detalle de los préstamos para la construcción del período</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Una fila por préstamo vigente en el período: N° de préstamo o contrato, tipo (Específico o General), activo u obra financiada (solo los específicos), descripción, importe del préstamo, tasa nominal anual, costo financiero del período realmente incurrido y, en los específicos, los rendimientos de la inversión temporal de esos fondos. Si no hubo inversión temporal, escriba 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa. Si su archivo usa otros nombres de columna, puede cargarlo igual: al procesar podrá mapear a mano dónde está cada dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EJEMPLO · datos ficticios</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Detalle de los préstamos para la construcción del período</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Una fila por préstamo vigente en el período: N° de préstamo o contrato, tipo (Específico o General), activo u obra financiada (solo los específicos), descripción, importe del préstamo, tasa nominal anual, costo financiero del período realmente incurrido y, en los específicos, los rendimientos de la inversión temporal de esos fondos. Si no hubo inversión temporal, escriba 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa sin cambiar los encabezados.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Obligatoria</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Qué va aquí (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>N° de préstamo o contrato</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Tipo (Específico / General)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Activo u obra financiada (solo los específicos)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Importe del préstamo vigente en el período</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Tasa nominal anual (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Costo financiero del período realmente incurrido</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Rendimientos de la inversión temporal de esos fondos (solo los específicos)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
